--- a/backend/Master_Tracker_Gemini.xlsx
+++ b/backend/Master_Tracker_Gemini.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,9 +552,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Prakash Kumar</t>
@@ -570,22 +567,14 @@
           <t>kumar.prakash.2112@gmail.com</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GlobalLogic</t>
+          <t>Publicis Sapient</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+        <v>1.58</v>
+      </c>
       <c r="R2" t="inlineStr">
         <is>
           <t>B.Tech</t>
@@ -596,26 +585,494 @@
           <t>Motilal Nehru National Institute Of Technology</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer</t>
+          <t>Associate Software Engineer 2</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Python, LLMs, GPT, Agentic AI, LangChain, LangGraph, Vector DBs, Deep Learning, CNN, AWS, RAG, AWS Bedrock, Lambda, API Gateway, C/C++, JavaScript, SQL, R, React.js, MySQL, Node.js, Web Development, GenAI, Machine Learning, Data Science, NLP, OOPs, DBMS, DSA, GitHub, VS Code, Jupyter Notebook, Docker, JIRA, Azure, GCP, NumPy, Pandas, Seaborn, Matplotlib, Scikit-Learn, CrewAI, Tensorflow, OpenCV, Keras</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+          <t>C/C++, JavaScript, SQL, Python, R, React.js, MySQL, Node.js, Web Development, GenAI, Machine Learning, Agentic AI, Data Science, NLP, OOPs, DBMS, DSA, GitHub, VS Code, Jpyter Notebook, Docker, JIRA software, AWS services, Azure services, GCP, NumPy, Pandas, Seaborn, Matplotlib, Scikit-Learn, Langchain, Langgraph, CrewAI, Tensorflow, OpenCV, Keras, LLMs, GPT, Vector DBs, Deep Learning, CNN, RAG, AWS Bedrock, Lambda, API Gateway, Amplify, AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SRISTI SUMAN</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>+91-7759989765</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>sristi.1128@gmail.com</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>DIAGEO</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Integrated M.Tech</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Central University of Jharkhand, India</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Python, SQL, PySpark, Supervised Learning, Unsupervised Learning, Regression, Random Forest, XG Boost, Time Series Models, Cross-validation, Precision, Recall, F1 score, Feature Selection, Feature Engineering, Pandas, Unity Catalog, Delta tables, Databricks, MLOps, DevOps, EDA, Data Preprocessing, Unstructured Data, Structured Data, Imbalanced Datasets, Power BI, DAX queries, Data Modeling, Excel, Pivot tables, Seaborn, Matplotlib, NLP, Text Preprocessing, Tokenization, Stemming, Lemmatization, Sentiment Analysis, Topic Modeling, LDA, LLM, RAG, Azure AI Foundry, Azure OpenAI, Vector Embeddings, Vector Search, Text Extraction, Delta Live Tables, Aera, Palantir</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AAHLAAD MUSUNURU</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>+91 9347565924</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>aahlaad1995@yahoo.com</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>UN ESCWA</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Rajahmundry, Andhra Pradesh, India</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Data Analyst Consultant</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>SQL, T-SQL, Power BI, DAX, SSIS, Data Warehousing, Dimensional Modelling, ETL Automation, Business Intelligence, Data Analytics, Dashboard Development, ETL Development, ETL Pipeline Optimization, SSAS, KPI Monitoring, Performance Analysis, Power BI Service, Power BI Data Gateway, DirectQuery, Microsoft SQL Server 2019, PostgreSQL, PostGIS, MDX, SQL Server Agent, Python, R, Git, GitHub, REST APIs, ODBC, QGIS, ArcGIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aakash Anand</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>+91 7805061140</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>aakash.anand83@gmail.com</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Infosys Consulting</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Medicaps University</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Consultant - AI Labs</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Generative AI, Agentic AI Systems, Multi-Agent Systems, AI Agent Orchestration, Tool Calling, RAG, Model Context Protocol (MCP), LLMs, Azure OpenAI, OpenAI APIs, LLaMAExtract, LLaMAParse, NVIDIA NIMS, CrewAI, LangChain, Vector Databases, Vector Search, Python, SQL, Databricks, Palantir Foundry, Azure, ADF, ADLS, Logic Apps, Cognitive Services, AWS, S3, CI/CD, Azure DevOps, Git, GPT models, GPT-5, SpaCy, NLTK, Logistic Regression, ANN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aarti Chauhan</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>+91 9899739226</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>aarti.c2004@gmail.com</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Cognizant Technology Solutions India Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>M.Tech</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>MDU University</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Senior Associate Projects</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Angular, JavaScript, TypeScript, HTML, CSS, React, Redux, Java, Spring, Hibernate, Php, Wordpress, InfusionSoft, Maven, Jira, Asana, Copilot, Jest, Mocha, Jasmine, Cypress, Git, BitBucket, GitLab, GitHub, Source Tree, SonarQube, ESLint, Jenkins, Bamboo, AWS, Azure, Dockers, MySQL, SQL, Oracle, Postgres, NoSQL, MongoDB, Reactive forms, NPM, Material-UI, .Net, Bootstrap, Admin LTE, Hbr-UI, JSP Schema, Neo4j, JQuery, NGX-Translate, Google Analytics, Google Dialog Flow, Engage, KTD, Stripe, Ingenico, Omise, Jasper Reports, CIBIL, Pan Card Validation, Android</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AARUSHI KOUL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>+919811229536</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>aarushikoul@gmail.com</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>madebyaarushi</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>B.A(H)English</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Lady Shri Ram College for Women, Delhi University</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Visual+Communication Designer&amp;Brand Strategist</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Asana, JIRA, Microsoft Office, Google Workspace, SQL, Python, CSS, JavaScript, HTML, React, Swift, GitHub, Tableau, Google Analytics, UserTesting, Lookback, SurveyMonkey, Adobe Premiere Pro, Davinci Resolve, Figma, Adobe Creative Cloud, Photoshop, Illustrator, XD, Product Strategy, Growth Marketing, Social Media Strategy, Partnership Management, Community Building, Brand Identity, Logo Design, Branding, Content Strategy, Communication Design, Product Marketing, Ad Campaigns, UI/UX Design, Event Management, Media Coverage, Photography, Filmography, Video Editing, Fundraising, Public Speaking, Workshop Facilitation, Sponsorship Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aashish</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7983480454</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>maasoom9211@gmail.com</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>GITS India Solutions Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Masters in Computer Science</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Woolf University California</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Python, SQL, Pandas, NumPy, Matplotlib, Seaborn, PySpark, LangChain, Hugging Face Transformers, Scikit-Learn, RAG Architecture, Multi-Agent Systems, Pinecone, ChromaDB, Mem0, AWS, Docker, GitHub Actions, CI/CD, FastAPI, Streamlit, Flask, Power BI, Tableau, Excel, Gsheets, VS Code, SQL Server, Google Big Query, Google Colab</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aayush Nair</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9893048149</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>aayushn128@gmail.com</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Falcon Autotech PVT LT</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Gurugram,Haryana,India</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Bachelor of Engineering</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Rajiv Gandhi Prodyogiki Vishwavidhyalay</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Team Lead Research And Development</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Python, Django, Restfull, Numpy, Sickitlearn, Tensorflow, Keras, OpenCV, Pandas, Seaborn, Matplotlib, Plotly, MongoDB, PostgreSQL, VisualStudioCode, Git, Pycharm, JupyterNotebook, Bigquery, CloudStorage, VertexAI, Dialogflowessentials, DailogflowCX, CloudFunction, AppEngine, GoogleSpeechAPI, Dataproc, Dataflow, DataStudio, NLP, Machine Learning, OCR, Image Processing, Linear Regression, Statistical Techniques</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Abhijeet Sengar</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>+ 91 - 7067618261</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>abhijeetsengar10@gmail.com</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Testyantra</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Gwalior, India</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>B. Tech</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>RGPV University</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Software Engineer - Python Developer</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Python, Django, Flask, FastAPI, Cloud, AWS Lambda, TypeScript, HTML, CSS, JavaScript, PostgreSQL, SQL, MongoDB, Docker, Postman, Github, Jira, AWS web services, SonarQube, FOSSA, Pandas, NumPy, Matplotlib, Communication</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Abhijeet Singh</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>+91 7007994663</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>abhi86048604@gmail.com</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LUMIQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Noida, India</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Master of Science</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>IIT Bombay</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Python, Pandas, Numpy, Scikit-Learn, Machine Learning, NLP, Transformers, Generative AI, CrewAI, FastAPI, Docker, SQL, AWS Bedrock, Sagemaker</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/Master_Tracker_Gemini.xlsx
+++ b/backend/Master_Tracker_Gemini.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1808" yWindow="1808" windowWidth="16199" windowHeight="9307" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +412,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AA15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col width="19.19921875" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1009,9 +1011,6 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Abhijeet Singh</t>
@@ -1027,7 +1026,6 @@
           <t>abhi86048604@gmail.com</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>LUMIQ</t>
@@ -1036,17 +1034,11 @@
       <c r="J11" t="n">
         <v>0.9</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Noida, India</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Master of Science</t>
@@ -1057,22 +1049,244 @@
           <t>IIT Bombay</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr">
         <is>
           <t>Python, Pandas, Numpy, Scikit-Learn, Machine Learning, NLP, Transformers, Generative AI, CrewAI, FastAPI, Docker, SQL, AWS Bedrock, Sagemaker</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ABHIJIT CHAKRABORTY</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>+91 8638752465</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>abhijityachak@gmail.com</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Halliburton</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>National Institute of Technology, Silchar</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Senior AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Large Language Models, LLMs, Retrieval-Augmented Generation, RAG, Prompt Engineering, LangChain, OpenAI API, Hugging Face Transformers, Chatbot &amp; Conversational AI Development, NLP, TensorFlow, PyTorch, Neural Networks, Anomaly Detection, Regression/Classification Models, ML Experiment Tracking, Weights &amp; Biases, GCP, AWS, Azure DevOps, Docker, CI/CD Pipelines, Git, Poetry, UV, Python, Golang, SQLServer, SQLite, SQLAlchemy, NumPy, Pandas, Databricks, Tkinter, Viktor.ai, LangGraph, ChromaDB, Gemini, FastAPI, Langfuse, Ragas, NeMo Guardrails, Sarvam AI, Ollama, sentence-transformers, Telegram Bot API, Redis, JWT, httpx, gRPC, PostgreSQL, RabbitMQ, Go, Next.js, React, Alembic, Prometheus, GitHub Actions, Ruff, pytest, Safety CLI, Render, Mage, Cloud Storage, BigQuery, dbt, Terraform, Looker Studio, MobileNetV2, TFLite, AWS Lambda, Kaggle, Scikit-learn, ML Classification, EDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Abhilash Thul</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>+91 7875211991</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>thul.abhilash@gmail.com</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Synopsys Inc</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Pune, Maharashtra</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Symbiosis International University</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Enterprise Solution Architect</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>LangChain, LlamaIndex, CrewAI, Anthropic Claude, Azure OpenAI, GPT-4, Prompt Engineering, RAG, Embeddings, Vector Databases, Microsoft Copilot Studio, Azure AI Services, Azure Cognitive Search, Power Platform AI Builder, MCP Client, MCP Server, Python, R, SQL, Alteryx, Pandas, Scikit-learn, NLP, Sentiment Analysis, Regression, Clustering, PCA, Power BI, Tableau, Plotly Dash, R Shiny, Azure, DevOps, Functions, Celonis, MongoDB, MySQL, REST APIs, Git, NIST AI RMF, EU AI Act, Agile, Scrum, RAGAS, Stanford CoreNLP, NLTK, TextBlob, SPSS, Selenium, BS4, SQLAlchemy, Red Hat</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Abhinandan Prajapati</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>+91-7408331278</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>sdeabhinandan@gmail.com</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Serviingo Technologies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Immediate Joiner</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Government Polytechnic Lucknow</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Node.js, Express.js, MongoDB, Postgresql, ReactJs, React Native, AWS, Nest.js, REST APIs, JavaScript, HTML5, CSS, Tailwind CSS, Context API, Zustand, Firebase, Redis, EC2, S3 Buckets, RDS, Route53, Netlify, Vercel, Render, Hostinger, Postman, GitHub, GitLab, Google Play Console, SEO, Google Search Console, Google Analytics, Google AdMob Integration, Google Adsense Integration, Cursor, Claude.ai, Copilot, Antigravity</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Abhinav Jha</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>+91 9074434534</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>abhinavjha0302@gmail.com</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Aarleo Technologies</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Bachelor of Engineering</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Samrat Ashok Technological Institute</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Hadoop, Hive, Spark, Python, Databricks, SQL, Scala, ADLS, ADF, Oracle, MYSQL, Apache Spark, HDFS, HBase, MapReduce, Sqoop, Spark-SQL, Unstructured API, Structured API, PySpark, Regex, Parquet, Databricks Workflows</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
